--- a/public/exports-from-60-with-coowners/29189633.xlsx
+++ b/public/exports-from-60-with-coowners/29189633.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365260</t>
+          <t xml:space="preserve">311365261</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366596</t>
+          <t xml:space="preserve">311366598</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366602</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366589</t>
+          <t xml:space="preserve">311366590</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -13039,7 +13039,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379031</t>
+          <t xml:space="preserve">311379034</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379054</t>
+          <t xml:space="preserve">311379055</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381685</t>
+          <t xml:space="preserve">311381687</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311387766</t>
+          <t xml:space="preserve">311396690</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189633.xlsx
+++ b/public/exports-from-60-with-coowners/29189633.xlsx
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365262</t>
+          <t xml:space="preserve">311365263</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365267</t>
+          <t xml:space="preserve">311365266</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365261</t>
+          <t xml:space="preserve">311365260</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366598</t>
+          <t xml:space="preserve">311366599</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366603</t>
+          <t xml:space="preserve">311366605</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366590</t>
+          <t xml:space="preserve">311366591</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366593</t>
+          <t xml:space="preserve">311366595</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379064</t>
+          <t xml:space="preserve">311379069</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379047</t>
+          <t xml:space="preserve">311379050</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311379055</t>
+          <t xml:space="preserve">311379059</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -15289,7 +15289,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311381687</t>
+          <t xml:space="preserve">311381685</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311396690</t>
+          <t xml:space="preserve">311387766</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -26014,7 +26014,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422167</t>
+          <t xml:space="preserve">311422168</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189633.xlsx
+++ b/public/exports-from-60-with-coowners/29189633.xlsx
@@ -9139,12 +9139,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365263</t>
+          <t xml:space="preserve">311365262</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -9214,12 +9214,12 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">311365266</t>
+          <t xml:space="preserve">311365267</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366605</t>
+          <t xml:space="preserve">311366603</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311366591</t>
+          <t xml:space="preserve">311366589</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -26014,7 +26014,7 @@
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422168</t>
+          <t xml:space="preserve">311422167</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
